--- a/Projektplanung.AMIR_SEBASTIANxlsx.xlsx
+++ b/Projektplanung.AMIR_SEBASTIANxlsx.xlsx
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="31">
   <si>
     <t xml:space="preserve">Projektname: </t>
   </si>
@@ -146,6 +146,9 @@
   </si>
   <si>
     <t>Testen aller Funktionen</t>
+  </si>
+  <si>
+    <t>ZSM</t>
   </si>
   <si>
     <t>GithHub Push + Commits Kontrollieren</t>
@@ -164,7 +167,7 @@
     <numFmt numFmtId="176" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* \-??\ &quot;€&quot;_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-* #,##0\ &quot;€&quot;_-;\-* #,##0\ &quot;€&quot;_-;_-* &quot;-&quot;\ &quot;€&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -174,13 +177,6 @@
     </font>
     <font>
       <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -342,7 +338,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -472,12 +468,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -894,148 +884,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1623,9 +1613,11 @@
         <v>40</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" s="14"/>
+        <v>14</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="12">
@@ -1640,7 +1632,9 @@
       <c r="D17" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="14"/>
+      <c r="E17" s="14" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="12">
@@ -1655,7 +1649,9 @@
       <c r="D18" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="14"/>
+      <c r="E18" s="14" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="12">
@@ -1668,16 +1664,18 @@
         <v>30</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="14"/>
+        <v>14</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="12">
         <v>15</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C20" s="13">
         <v>30</v>
@@ -1685,14 +1683,16 @@
       <c r="D20" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E20" s="14"/>
+      <c r="E20" s="14" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="12">
         <v>16</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C21" s="13">
         <v>30</v>
